--- a/static/data/database/SS2_Students.xlsx
+++ b/static/data/database/SS2_Students.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SS2 Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SS2 Students'!$A$1:$H$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SS2 Students'!$A$1:$H$114</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H118"/>
+  <dimension ref="A1:H114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -473,27 +473,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>std347</t>
+          <t>std234</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WESLEY</t>
+          <t>ADEYEMI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DESTINY</t>
+          <t>FUAD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SOLOMON</t>
+          <t>FAUZAN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>08066364578</t>
+          <t>07060774164</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -515,32 +515,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>std348</t>
+          <t>std235</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>IBRAHIM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ZAINAB</t>
+          <t>ADAM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BULAWUS</t>
+          <t>ZAID</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>08166884483</t>
+          <t>08132389615</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -557,32 +557,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>std349</t>
+          <t>std236</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>ISAH</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RUKAYYAH</t>
+          <t>ABBAS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SANUSI</t>
+          <t>AHMAD</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>08037760678</t>
+          <t>09130680040</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -599,32 +599,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>std350</t>
+          <t>std237</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>YUSUF</t>
+          <t>KAKILI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FAIZA</t>
+          <t>ALIYU</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ANJOLA</t>
+          <t>ASHRAF</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>08035554245</t>
+          <t>08035115628</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -641,32 +641,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>std351</t>
+          <t>std238</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SALIHU</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NASIRAT</t>
+          <t>TIJJANI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AJOKE</t>
+          <t>UMAR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0813635719</t>
+          <t>08036065686</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -683,32 +683,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>std352</t>
+          <t>std239</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADEYEMI</t>
+          <t>YAHAYA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SUI'AD</t>
+          <t>MAARA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ADEDOLAPO</t>
+          <t>UMAR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>08057744112</t>
+          <t>07067509810</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -725,32 +725,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>std353</t>
+          <t>std240</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ABBAKURA</t>
+          <t>ABDULQADIR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ZAYNAB</t>
+          <t>TEMITOPE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ALI</t>
+          <t>UTHMAN</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>08032409318</t>
+          <t>08023826740</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -767,32 +767,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>std354</t>
+          <t>std241</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HAUWA'U</t>
+          <t>IBRAHIM</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ABBAS</t>
+          <t>MUSA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>08068172056</t>
+          <t>08032140551</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -809,32 +809,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>std355</t>
+          <t>std242</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EGYOM</t>
+          <t>SHEHU</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MARYAM</t>
+          <t>AHMAD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>YACUB</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>08037821441</t>
+          <t>08066027728</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -851,28 +851,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>std356</t>
+          <t>std243</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UMAR</t>
+          <t>TUKUR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HAUWA</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AL-AMIN</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>08064640161</t>
+          <t>08184501992</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -889,27 +893,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>std357</t>
+          <t>std244</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LAWAL</t>
+          <t>YUSUF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FAIZA</t>
+          <t>SALIHU</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OMOTO'BA</t>
+          <t>MARYAM M.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>08039550055</t>
+          <t>08037567178</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -931,27 +935,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>std358</t>
+          <t>std245</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SALIHU</t>
+          <t>ALIYU</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BILKISU</t>
+          <t>ASHEZI</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SANI</t>
+          <t>YASMIN</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>09158872545</t>
+          <t>08066686000</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -973,27 +977,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>std359</t>
+          <t>std246</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>KOLE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RABIAT</t>
+          <t>MUHAMMED</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MUKHTAR</t>
+          <t>HAFSAT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>07063326189</t>
+          <t>08140739244</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1015,27 +1019,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>std360</t>
+          <t>std247</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ADETORO</t>
+          <t>AMINU</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ARAFAT</t>
+          <t>MSHEELIA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ADEOLA</t>
+          <t>KHADIJAH</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>08005426862</t>
+          <t>08033155739</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1057,27 +1061,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>std361</t>
+          <t>std248</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>OYENIYI</t>
+          <t>GBADAMOSI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MUMINAT</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>OLAYINKA</t>
-        </is>
-      </c>
+          <t>RASHEEDAH</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>08034411946</t>
+          <t>08035872403</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1099,27 +1099,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>std362</t>
+          <t>std249</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HASSAN</t>
+          <t>DIKKO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MUHSINAH</t>
+          <t>ISMAIL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ABDULLAHI</t>
+          <t>FATIMA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>08093316129</t>
+          <t>08081955353</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1141,28 +1141,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>std363</t>
+          <t>std250</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ISHAQ</t>
+          <t>KABIDO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ABDULRAHMAN</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>MUSA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>RAHAMA</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>08036013758</t>
+          <t>08138424118</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1179,32 +1183,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>std364</t>
+          <t>std251</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ISHAQ</t>
+          <t>ADEROGBA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UMAR</t>
+          <t>ADELESO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FAROUQ</t>
+          <t>HASSANA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>08028151955</t>
+          <t>08038204448</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1221,32 +1225,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>std365</t>
+          <t>std252</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HARUNA</t>
+          <t>ADEMOYE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>ABIOLA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AL-AMIN</t>
+          <t>FATHIA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>08065329175</t>
+          <t>08038184758</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1263,32 +1267,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>std366</t>
+          <t>std253</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ABUBAKAR</t>
+          <t>YAHAYA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SADIQ</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TAOFEEQ</t>
+          <t>AISHA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>07035983882</t>
+          <t>07063498835</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1305,32 +1309,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>std367</t>
+          <t>std254</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>KABIR</t>
+          <t>YUSUF</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ABUBAKAR</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MUSA</t>
+          <t>MUFIDAT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>08036344620</t>
+          <t>07064220549</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1347,32 +1351,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>std368</t>
+          <t>std255</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KAWU</t>
+          <t>ISMAIL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AHMAD</t>
+          <t>ISAH</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TUKUR</t>
+          <t>FAIZA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>08055402382</t>
+          <t>07063619332</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1389,32 +1393,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>std369</t>
+          <t>std256</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MAHMUD</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>EFUA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>AMIRA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>07035553555</t>
+          <t>08033410008</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1431,28 +1435,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>std370</t>
+          <t>std257</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MOMOH</t>
+          <t>OMADEFU</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TESLIM</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>ASIBI</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AMIRA</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>08035877447</t>
+          <t>08036057258</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1469,28 +1477,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>std371</t>
+          <t>std258</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>ADEYEMI</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ABDULMALIK</t>
+          <t>HEBBAHTULLAH</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>07059477616</t>
+          <t>08036261741</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1507,32 +1515,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>std372</t>
+          <t>std259</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>USMAN</t>
+          <t>DAMUSA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ISMAIL</t>
+          <t>UFEDOTOH</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MUSA</t>
+          <t>NANA K.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>07035673797</t>
+          <t>08065376751</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1549,32 +1557,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>std373</t>
+          <t>std260</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AHMAD</t>
+          <t>GALADIMA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ABUBAKAR</t>
+          <t>USMAN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>JANYAU</t>
+          <t>KHADIJA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>07077246902</t>
+          <t>08144826092</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1591,32 +1599,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>std374</t>
+          <t>std261</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UMAR</t>
+          <t>ABUBAKAR</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IDRIS</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>ATIKU</t>
-        </is>
-      </c>
+          <t>UMMULKHAIR</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>08026197229</t>
+          <t>08030569524</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1633,27 +1637,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>std375</t>
+          <t>std262</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ABDULGHAFFAR</t>
+          <t>TAJUDEEN</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>M.</t>
+          <t>ASIWAJU</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>KHALID</t>
+          <t>ABDULBASIT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>09033362393</t>
+          <t>080095613348</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1663,7 +1667,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SS2_SILVER</t>
+          <t>SS2_DIAMOND</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1675,37 +1679,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>std376</t>
+          <t>std263</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>MUHAMMED</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>JAMEEL</t>
+          <t>OYIZA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ABUBAKAR</t>
+          <t>KHAIRET</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>08035573720</t>
+          <t>08072424291</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SS2_SILVER</t>
+          <t>SS2_DIAMOND</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1717,27 +1721,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>std377</t>
+          <t>std264</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ABDULHAFIZ</t>
+          <t>HABIBULLAH</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ISMAIL</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>MOMBO</t>
-        </is>
-      </c>
+          <t>ABDULMALIK</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>08035972744</t>
+          <t>08065544064</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SS2_SILVER</t>
+          <t>SS2_DIAMOND</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1759,27 +1759,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>std378</t>
+          <t>std265</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IBRAHIM</t>
+          <t>BABAKURA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ALIYU</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>MUSA</t>
-        </is>
-      </c>
+          <t>TIJJANI</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>08166646064</t>
+          <t>08067045013</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1801,27 +1797,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>std379</t>
+          <t>std266</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FAREED</t>
+          <t>MUSA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ABDURRASHEED</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>ABIOLA</t>
-        </is>
-      </c>
+          <t>TAHIR</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>08035553999</t>
+          <t>08066441344</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1843,23 +1835,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>std380</t>
+          <t>std267</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RAYYAN</t>
+          <t>KABIR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>OLATUNJI</t>
+          <t>SAIDUBABA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>07030405026</t>
+          <t>09119851571</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1881,27 +1873,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>std381</t>
+          <t>std268</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MUKTAR</t>
+          <t>SHEHU</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IBRAHIM</t>
+          <t>RAMALAN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ADAM</t>
+          <t>SAABIR</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>08066077464</t>
+          <t>08035927011</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1923,27 +1915,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>std382</t>
+          <t>std269</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SA'AD</t>
+          <t>AL-AMIN</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IDRIS</t>
+          <t>O.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ODARIKO</t>
+          <t>AHMED</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>08036330223</t>
+          <t>08136552705</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1965,27 +1957,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>std383</t>
+          <t>std270</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>ZAHARADEEN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>JAMIU</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>SULEIMAN</t>
-        </is>
-      </c>
+          <t>UMAR</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>08016685769</t>
+          <t>08035944688</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2007,32 +1995,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>std384</t>
+          <t>std271</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HAFSAT</t>
+          <t>AMINU</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>UMAR</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ZAKARI</t>
+          <t>MUSA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>080354501362</t>
+          <t>08032889558</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2049,28 +2037,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>std385</t>
+          <t>std272</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BARAKALLAH</t>
+          <t>SADIQ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AKINIBORODE</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>ISMAIL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>IBRAHIM</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>08032567133</t>
+          <t>08033587358</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2087,23 +2079,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>std386</t>
+          <t>std273</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MARYAM</t>
+          <t>YUSUF</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SULEIMAN</t>
+          <t>JAMILA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>07035501136</t>
+          <t>08036272740</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2125,23 +2117,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>std387</t>
+          <t>std274</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BARAKA</t>
+          <t>ABDURRAHMAN</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>OLAPADE</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>NUMAT</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>MAIMUNAT</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>080169485071</t>
+          <t>08036040662</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2163,27 +2159,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>std388</t>
+          <t>std275</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NIMAH</t>
+          <t>SAMBO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MIKAIL</t>
+          <t>HAJARA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>AMINU</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>08035559354</t>
+          <t>08035887544</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2205,27 +2201,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>std389</t>
+          <t>std276</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>SANI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>YUMNA</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ILIYASU</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>08036761254</t>
+          <t>07036576765</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2247,27 +2243,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>std390</t>
+          <t>std277</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SABO</t>
+          <t>SALISU</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AMINA</t>
+          <t>NANA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>ASMAU</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>07013237225</t>
+          <t>07089903318</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2289,23 +2285,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>std391</t>
+          <t>std278</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ABUBAKAR</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MAIMUNA</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>ZAINAB</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AMINU</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>08023931387</t>
+          <t>08055262097</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2327,27 +2327,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>std392</t>
+          <t>std279</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>YAHAYA</t>
+          <t>AMATULLAH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>YASMIN</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>YUNUSA</t>
-        </is>
-      </c>
+          <t>ABDULMALIK</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>08025589912</t>
+          <t>08036495912</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2369,27 +2365,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>std393</t>
+          <t>std280</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HASSAN</t>
+          <t>IKAKA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ASMAU</t>
+          <t>AHMED</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ISAH</t>
+          <t>BILKISU</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>07035995995</t>
+          <t>08033884440</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2411,32 +2407,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>std394</t>
+          <t>std281</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HAMISU</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MUFIDA</t>
+          <t>KABIR</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ZANGO</t>
+          <t>MUKHTAR</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>07036972559</t>
+          <t>08033912352</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2453,27 +2449,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>std395</t>
+          <t>std282</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MUBARAK</t>
+          <t>ABDULLAHI</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>IBRAHIM</t>
-        </is>
-      </c>
+          <t>HUSSAIN</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>09031216070</t>
+          <t>07035663576</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2495,27 +2487,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>std396</t>
+          <t>std283</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>BASHIR</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>KABEER</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>IBRAHIM</t>
-        </is>
-      </c>
+          <t>MAHMUD</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>08003700659</t>
+          <t>08032181310</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2537,27 +2525,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>std397</t>
+          <t>std284</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NASIR</t>
+          <t>AMINU</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SA'IDU</t>
+          <t>YASSAR</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>IBRAHIM</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>07045077809</t>
+          <t>08157275454</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2579,37 +2567,33 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>std398</t>
+          <t>std285</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>YUSUF</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AISHA</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>RABIU</t>
-        </is>
-      </c>
+          <t>SA'AD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>07025646735</t>
+          <t>08034000882</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SS2_SILVER</t>
+          <t>SS2_GOLD</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2621,37 +2605,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>std399</t>
+          <t>std286</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>ABAHI</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AMADULLAH</t>
+          <t>WONDA</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NJOBDI</t>
+          <t>U. ABDULSAMAD</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>080025521562</t>
+          <t>08066188131</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SS2_SILVER</t>
+          <t>SS2_GOLD</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2663,37 +2647,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>std400</t>
+          <t>std287</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>SHETTIMA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SAFIYA</t>
+          <t>B.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LOKO</t>
+          <t>MUSTAPHA</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>08033441055</t>
+          <t>08026994119</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SS2_SILVER</t>
+          <t>SS2_GOLD</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2705,27 +2689,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>std401</t>
+          <t>std288</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ABDULHAMEED</t>
+          <t>ADEYEMI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>HASSAN</t>
+          <t>MATTHEW</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NAIBI</t>
+          <t>ADESIRE</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>08005127892</t>
+          <t>08032190197</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2735,7 +2719,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SS2_SILVER</t>
+          <t>SS2_GOLD</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2747,23 +2731,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>std402</t>
+          <t>std289</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ANISA</t>
+          <t>KHAIRAT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NASIR</t>
+          <t>BADAMASI</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>08135850029</t>
+          <t>08032245423</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2773,7 +2757,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SS2_SILVER</t>
+          <t>SS2_GOLD</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2785,7 +2769,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>std403</t>
+          <t>std290</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2795,13 +2779,13 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>UMAR</t>
+          <t>SULEIMAN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>09136167237</t>
+          <t>07029636558</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2811,7 +2795,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SS2_SILVER</t>
+          <t>SS2_GOLD</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2823,23 +2807,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>std404</t>
+          <t>std291</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FA'IZ</t>
+          <t>ABDULLAHI</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>HUSNA</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>UMAIMAH</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ZHEOMA</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0703300155</t>
+          <t>08035885141</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2849,7 +2837,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SS2_SILVER</t>
+          <t>SS2_GOLD</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2861,23 +2849,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>std405</t>
+          <t>std292</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ABDULMUMIN</t>
+          <t>SAED</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ABDULMALIK</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>ABUBAKAR</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>HASSAN</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>08094974743</t>
+          <t>08035973912</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2899,23 +2891,23 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>std406</t>
+          <t>std293</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>OHUI</t>
+          <t>AKINLOYE</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MOSES</t>
+          <t>GODSWILL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>08128187444</t>
+          <t>08069353822</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2937,32 +2929,28 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>std407</t>
+          <t>std294</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ABUBAKAR</t>
+          <t>RUKAYYA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ALAMIN</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>ABDULLAHI</t>
-        </is>
-      </c>
+          <t>IBRAHIM</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>07045413365</t>
+          <t>08027163415</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2979,28 +2967,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>std408</t>
+          <t>std295</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ALI</t>
+          <t>FARZEENAH</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FAHEEM</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>T.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>08065490010</t>
+          <t>08033577423</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3017,28 +3009,28 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>std409</t>
+          <t>std296</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DANJUMA</t>
+          <t>OLAGUNJU</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ARAFAH</t>
+          <t>FIRDAUS</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>09041645172</t>
+          <t>08138369857</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3055,32 +3047,28 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>std410</t>
+          <t>std297</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ABUBAKAR</t>
+          <t>OLUFEMOH</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AHMAD</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>PINDAR</t>
-        </is>
-      </c>
+          <t>MUNIRAT</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>08035204272</t>
+          <t>08026160230</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3097,28 +3085,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>std411</t>
+          <t>std298</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AUDU</t>
+          <t>KHADIJAH</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ABDULHAMID</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>BABAYARO</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>MUKHTAR</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>08032741681</t>
+          <t>07063104355</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3135,32 +3127,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>std412</t>
+          <t>std299</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AMMDA</t>
+          <t>SABIRAH</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ABUBAKAR</t>
+          <t>HASSAN</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>IMRAN</t>
+          <t>ABDULLAH</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>08038976432</t>
+          <t>08034204648</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3177,23 +3169,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>std413</t>
+          <t>std300</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MUHAMMED</t>
+          <t>ABUBAKAR</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>HUSSEIN</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>AMINU</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>SANJUMA</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>08037548555</t>
+          <t>08034132060</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3215,23 +3211,23 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>std414</t>
+          <t>std301</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FARUK</t>
+          <t>IBRAHIM</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MUSA</t>
+          <t>TAHIR</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>08056603644</t>
+          <t>07035485005</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3253,27 +3249,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>std415</t>
+          <t>std302</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SHAMSHUDEEN</t>
+          <t>KOREDE</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ALIYU</t>
+          <t>SALAU</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>RABO</t>
+          <t>ABDULLAHI</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>08131834642</t>
+          <t>08166294250</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3295,32 +3291,28 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>std416</t>
+          <t>std303</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HALIMA</t>
+          <t>ZANSHIRU</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IBRAHIM</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>MUSTAPHA</t>
-        </is>
-      </c>
+          <t>YUSUF</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>08033550857</t>
+          <t>08072602070</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3337,23 +3329,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>std417</t>
+          <t>std304</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BAKO-BABS</t>
+          <t>JUNAIRIYYA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SAMEENA</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>RABIU</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>IDRIS</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>08027431000</t>
+          <t>07039229772</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3375,27 +3371,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>std418</t>
+          <t>std305</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>OPARIKO</t>
+          <t>ABUBAKAR</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SA'ADATU</t>
+          <t>FATIMA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>IDRIS</t>
+          <t>JASMINE</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>08036330773</t>
+          <t>08033365925</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3417,28 +3413,32 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>std419</t>
+          <t>std306</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BABANGIDA</t>
+          <t>ABDULMALIK</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>UMAR</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>SAMIR</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AHMAD</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>07017917835</t>
+          <t>08057265792</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3455,7 +3455,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>std420</t>
+          <t>std307</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MARYAM</t>
+          <t>AISHA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>08033293137</t>
+          <t>08036173202</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3497,27 +3497,23 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>std421</t>
+          <t>std308</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ABDULLAHI</t>
+          <t>BENITA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AISHA</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>SAMBO</t>
-        </is>
-      </c>
+          <t>PETER</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>08062843138</t>
+          <t>08069102556</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3539,32 +3535,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>std422</t>
+          <t>std309</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>ISHAQ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>HAJARA</t>
+          <t>A.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>KABIR</t>
+          <t>QASIM USMAN</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>08069453726</t>
+          <t>08033191149</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3581,32 +3577,28 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>std423</t>
+          <t>std310</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NENZAR</t>
+          <t>MUHAMMED</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>REJOICE</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>KASSEM</t>
-        </is>
-      </c>
+          <t>SHEHU</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>08139187704</t>
+          <t>080062447500</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3623,28 +3615,28 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>std424</t>
+          <t>std311</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>YAKUBU</t>
+          <t>LUQMAN</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ASMAUABDULLAHI</t>
+          <t>ALAMIN</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>08035369624</t>
+          <t>07032620527</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3661,27 +3653,23 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>std425</t>
+          <t>std312</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LUKMAN</t>
+          <t>ABUBAKAR</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MARYAM</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>HANNAFA</t>
-        </is>
-      </c>
+          <t>HABIBA</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>07043716151</t>
+          <t>08041326079</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3703,23 +3691,23 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>std426</t>
+          <t>std313</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ABDULLAHI</t>
+          <t>MUSTAPHA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>HARRAIYA</t>
+          <t>FATIMA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>07081365050</t>
+          <t>08067757775</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3741,23 +3729,23 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>std427</t>
+          <t>std314</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>YUSUF</t>
+          <t>SANI</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>HAFSAH</t>
+          <t>FAZEELAT</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>08036278760</t>
+          <t>08030799725</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3767,7 +3755,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3779,27 +3767,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>std428</t>
+          <t>std315</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>YUSUF</t>
+          <t>SHOFOLUWE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ASMAU</t>
+          <t>O.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>JAJI</t>
+          <t>NEEMATULLAH</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>080698111313</t>
+          <t>07066229010</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3809,7 +3797,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3821,27 +3809,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>std429</t>
+          <t>std316</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ABUBAKAR</t>
+          <t>ABBA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AMINA</t>
+          <t>MAMMAN</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>JANYAU</t>
+          <t>FATIMA</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>07077266802</t>
+          <t>08039725582</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3851,7 +3839,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3863,37 +3851,37 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>std430</t>
+          <t>std317</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>FUAD</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FAUZIYA</t>
+          <t>ADEYEMI</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>GALADIMA</t>
+          <t>FAUZI</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>08039151906</t>
+          <t>080130680040</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3905,23 +3893,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>std431</t>
+          <t>std318</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FARUK</t>
+          <t>BASHIR</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ABDULKAREEM</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>ABDULLAHI</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>08036148800</t>
+          <t>080372667696</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3931,7 +3923,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3943,33 +3935,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>std432</t>
+          <t>std319</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AHMED</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AMINA</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
+          <t>MARAFIA</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ATTAHIR</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0916301143</t>
+          <t>0817808006</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3981,33 +3977,37 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>std433</t>
+          <t>std320</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PIUS</t>
+          <t>ADEBAYO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
+          <t>DAMILOLA</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>FATHIA</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0813224775</t>
+          <t>090388330432</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4019,23 +4019,27 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>std434</t>
+          <t>std321</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ISSA</t>
+          <t>SHAMSU</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MUSTAPHA</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
+          <t>ZIYAHULLHAQ</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0806359444</t>
+          <t>08037031114</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4045,7 +4049,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4057,23 +4061,23 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>std435</t>
+          <t>std322</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>IDOWU</t>
+          <t>JOHN</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ABDULBASIT</t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>08036888250</t>
+          <t>08034414206</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4095,23 +4099,23 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>std436</t>
+          <t>std323</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ADEYEMI</t>
+          <t>KOREDE</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TIAMIYU</t>
+          <t>SAMUEL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>08067771845</t>
+          <t>07053262036</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4133,27 +4137,23 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>std437</t>
+          <t>std324</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>AJAO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SENO</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>HASSAN</t>
-        </is>
-      </c>
+          <t>UMAR</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>07038666604</t>
+          <t>07034372559</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4175,27 +4175,27 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>std438</t>
+          <t>std325</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>AHMAD</t>
+          <t>ABDULLAHI</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ZUBAIRU</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>AHMAD</t>
+          <t>ALIYU</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>08033117355</t>
+          <t>080369891390</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4217,27 +4217,27 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>std439</t>
+          <t>std326</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MUSA</t>
+          <t>FARUK</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>UMAR</t>
+          <t>NDAYAKO</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>UMAR</t>
+          <t>SHAFI</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>07031940246</t>
+          <t>08032013860</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4259,27 +4259,27 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>std440</t>
+          <t>std327</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>AMINU</t>
+          <t>SANI</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>JAMOH</t>
+          <t>WAKILI</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>UMAR</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>07027266014</t>
+          <t>080331541112</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4301,28 +4301,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>std441</t>
+          <t>std328</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>IBRAHIM</t>
+          <t>ADEYEMI</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AUWAL</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>ADENIKE</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NAJA'A</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>08077229624</t>
+          <t>08067371845</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4339,32 +4343,28 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>std442</t>
+          <t>std329</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TIJJANI</t>
+          <t>AJAO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>YAHAYA</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>FAISAL</t>
-        </is>
-      </c>
+          <t>FAUZIYA</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>08036142876</t>
+          <t>08034372559</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4381,27 +4381,27 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>std443</t>
+          <t>std330</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ALI</t>
+          <t>ABDULLAHI</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>FOLA</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>JAMAL</t>
+          <t>SADIQ</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>08065490010</t>
+          <t>08036989390</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4423,27 +4423,27 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>std444</t>
+          <t>std331</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>KABIR</t>
+          <t>HASHIM</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USMAN</t>
+          <t>MUHAMMED</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ABDULRAHMAN</t>
+          <t>YUNUS</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>08055459291</t>
+          <t>08094198290</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4465,32 +4465,28 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>std445</t>
+          <t>std332</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
+          <t>UMAR</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
           <t>MUHAMMAD</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>TUMALA</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>ZAINAB</t>
-        </is>
-      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>08060726243</t>
+          <t>08037876862</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4507,27 +4503,23 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>std446</t>
+          <t>std333</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>YUSUF</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>BAYERO</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>SA'ADATU</t>
-        </is>
-      </c>
+          <t>HAUWA</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>08052144414</t>
+          <t>080359150327</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4549,27 +4541,23 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>std447</t>
+          <t>std334</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ABDURRAHMAN</t>
+          <t>SANUSI</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>NANA</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>FIRDAUSI</t>
-        </is>
-      </c>
+          <t>SUMAYYA</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>08029993984</t>
+          <t>08059706494</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4591,27 +4579,27 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>std448</t>
+          <t>std335</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MAMMAN</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>YUSHAU</t>
+          <t>MARYAM</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>HAFSAT</t>
+          <t>MADINAH</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>08035126935</t>
+          <t>08188720987</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4633,32 +4621,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>std449</t>
+          <t>std336</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>IBRAHIM</t>
+          <t>AMINU</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ABDULMUMIN</t>
+          <t>YASSAR</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>RAIHANA</t>
+          <t>USMAN</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>08032281992</t>
+          <t>091338237</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4675,32 +4663,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>std450</t>
+          <t>std337</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MURTALA</t>
+          <t>MUSBAHU</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FORTY</t>
+          <t>YAKUBU</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>FOUR MARZOOQAH</t>
+          <t>AHMAD</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>08142244844</t>
+          <t>080552442908</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4717,32 +4705,28 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>std451</t>
+          <t>std338</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>ZAYYAN</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ABDUL-AZIZ</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>SALMA</t>
-        </is>
-      </c>
+          <t>MUHSIN</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>08065486620</t>
+          <t>07068866548</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4759,32 +4743,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>std452</t>
+          <t>std339</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ADAM</t>
+          <t>ADESHINA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>KASIM</t>
+          <t>CASSANDRA</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>FARUK</t>
+          <t>HABIBA</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>08033121013</t>
+          <t>0817251384</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4801,32 +4785,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>std453</t>
+          <t>std340</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>YUSUF</t>
+          <t>BASHIR</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>IBRAHIM</t>
+          <t>MAHMUD</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ADAMU</t>
+          <t>HAUWA</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>08032209734</t>
+          <t>08036587954</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4843,32 +4827,28 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>std454</t>
+          <t>std341</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>HASSAN</t>
+          <t>ALIYU</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>LODDO</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>HAUWA</t>
-        </is>
-      </c>
+          <t>AHMAD</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>07038166600</t>
+          <t>08085566519</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4885,32 +4865,32 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>std455</t>
+          <t>std342</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>YAKUBU</t>
+          <t>ALIYU</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>DOMA</t>
+          <t>LOLO</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ALIYU SULTAN</t>
+          <t>FATIHA</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>08030173092</t>
+          <t>08035899950</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4927,32 +4907,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>std456</t>
+          <t>std343</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MUSA</t>
+          <t>ALIYU</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SHEHU</t>
+          <t>SHAFI</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>AISHA</t>
+          <t>UMAR</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>08034918426</t>
+          <t>0707306375</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4969,27 +4949,27 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>std457</t>
+          <t>std344</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>GOJI</t>
+          <t>ALHASSAN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>AALIYAH</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>FATIMA</t>
+          <t>UMMT</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>08036257991</t>
+          <t>080550885141</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5011,32 +4991,32 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>std458</t>
+          <t>std345</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SIAKA</t>
+          <t>ABUBAKAR</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SALAMI</t>
+          <t>AMAL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>JIBRIL</t>
+          <t>AISHA</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>08025512089</t>
+          <t>0803159021</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -5053,32 +5033,28 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>std459</t>
+          <t>std346</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>JIBRIL</t>
+          <t>SANUSI</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>BILKISU</t>
-        </is>
-      </c>
+          <t>ABDULRAHMAN</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>08033339229</t>
+          <t>08020850490</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -5092,176 +5068,8 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>std460</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>IBRAHIM</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>SULEIMURI</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>ZAYNAB</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>08035225745</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>std461</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>ADETOBO</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>ARAFAT</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>ADEOLA</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>08054266802</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>std462</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>ADAM</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>IDRIS</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>KOGO</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>08036223580</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>std463</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>MOHAMMAD</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>HASIZ</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>YUSUF</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>08060683287</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H118"/>
+  <autoFilter ref="A1:H114"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/static/data/database/SS2_Students.xlsx
+++ b/static/data/database/SS2_Students.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SS2 Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SS2 Students'!$A$1:$H$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SS2 Students'!$A$1:$H$118</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H114"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -473,27 +473,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>std234</t>
+          <t>std347</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ADEYEMI</t>
+          <t>WESLEY</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FUAD</t>
+          <t>DESTINY</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FAUZAN</t>
+          <t>SOLOMON</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>07060774164</t>
+          <t>08066364578</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -515,32 +515,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>std235</t>
+          <t>std348</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IBRAHIM</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ADAM</t>
+          <t>ZAINAB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ZAID</t>
+          <t>BULAWUS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>08132389615</t>
+          <t>08166884483</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -557,32 +557,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>std236</t>
+          <t>std349</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ISAH</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ABBAS</t>
+          <t>RUKAYYAH</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AHMAD</t>
+          <t>SANUSI</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>09130680040</t>
+          <t>08037760678</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -599,32 +599,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>std237</t>
+          <t>std350</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KAKILI</t>
+          <t>YUSUF</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ALIYU</t>
+          <t>FAIZA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ASHRAF</t>
+          <t>ANJOLA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>08035115628</t>
+          <t>08035554245</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -641,32 +641,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>std238</t>
+          <t>std351</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>SALIHU</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TIJJANI</t>
+          <t>NASIRAT</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>UMAR</t>
+          <t>AJOKE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>08036065686</t>
+          <t>0813635719</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -683,32 +683,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>std239</t>
+          <t>std352</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YAHAYA</t>
+          <t>ADEYEMI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MAARA</t>
+          <t>SUI'AD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>UMAR</t>
+          <t>ADEDOLAPO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>07067509810</t>
+          <t>08057744112</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -725,32 +725,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>std240</t>
+          <t>std353</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ABDULQADIR</t>
+          <t>ABBAKURA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TEMITOPE</t>
+          <t>ZAYNAB</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>UTHMAN</t>
+          <t>ALI</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>08023826740</t>
+          <t>08032409318</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -767,32 +767,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>std241</t>
+          <t>std354</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IBRAHIM</t>
+          <t>HAUWA'U</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MUSA</t>
+          <t>ABBAS</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>08032140551</t>
+          <t>08068172056</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -809,32 +809,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>std242</t>
+          <t>std355</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SHEHU</t>
+          <t>EGYOM</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AHMAD</t>
+          <t>MARYAM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>YACUB</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>08066027728</t>
+          <t>08037821441</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -851,32 +851,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>std243</t>
+          <t>std356</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TUKUR</t>
+          <t>UMAR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>AL-AMIN</t>
-        </is>
-      </c>
+          <t>HAUWA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>08184501992</t>
+          <t>08064640161</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -893,27 +889,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>std244</t>
+          <t>std357</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>YUSUF</t>
+          <t>LAWAL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SALIHU</t>
+          <t>FAIZA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MARYAM M.</t>
+          <t>OMOTO'BA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>08037567178</t>
+          <t>08039550055</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -935,27 +931,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>std245</t>
+          <t>std358</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ALIYU</t>
+          <t>SALIHU</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ASHEZI</t>
+          <t>BILKISU</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>YASMIN</t>
+          <t>SANI</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>08066686000</t>
+          <t>09158872545</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -977,27 +973,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>std246</t>
+          <t>std359</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KOLE</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MUHAMMED</t>
+          <t>RABIAT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>HAFSAT</t>
+          <t>MUKHTAR</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>08140739244</t>
+          <t>07063326189</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1019,27 +1015,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>std247</t>
+          <t>std360</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AMINU</t>
+          <t>ADETORO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MSHEELIA</t>
+          <t>ARAFAT</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>KHADIJAH</t>
+          <t>ADEOLA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>08033155739</t>
+          <t>08005426862</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1061,23 +1057,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>std248</t>
+          <t>std361</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GBADAMOSI</t>
+          <t>OYENIYI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RASHEEDAH</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>MUMINAT</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>OLAYINKA</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>08035872403</t>
+          <t>08034411946</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1099,27 +1099,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>std249</t>
+          <t>std362</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DIKKO</t>
+          <t>HASSAN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ISMAIL</t>
+          <t>MUHSINAH</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FATIMA</t>
+          <t>ABDULLAHI</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>08081955353</t>
+          <t>08093316129</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1141,32 +1141,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>std250</t>
+          <t>std363</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>KABIDO</t>
+          <t>ISHAQ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MUSA</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>RAHAMA</t>
-        </is>
-      </c>
+          <t>ABDULRAHMAN</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>08138424118</t>
+          <t>08036013758</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1183,32 +1179,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>std251</t>
+          <t>std364</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ADEROGBA</t>
+          <t>ISHAQ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ADELESO</t>
+          <t>UMAR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HASSANA</t>
+          <t>FAROUQ</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>08038204448</t>
+          <t>08028151955</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1225,32 +1221,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>std252</t>
+          <t>std365</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ADEMOYE</t>
+          <t>HARUNA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ABIOLA</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FATHIA</t>
+          <t>AL-AMIN</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>08038184758</t>
+          <t>08065329175</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1267,32 +1263,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>std253</t>
+          <t>std366</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>YAHAYA</t>
+          <t>ABUBAKAR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>SADIQ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>AISHA</t>
+          <t>TAOFEEQ</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>07063498835</t>
+          <t>07035983882</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1309,32 +1305,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>std254</t>
+          <t>std367</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>YUSUF</t>
+          <t>KABIR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>ABUBAKAR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MUFIDAT</t>
+          <t>MUSA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>07064220549</t>
+          <t>08036344620</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1351,32 +1347,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>std255</t>
+          <t>std368</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ISMAIL</t>
+          <t>KAWU</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ISAH</t>
+          <t>AHMAD</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FAIZA</t>
+          <t>TUKUR</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>07063619332</t>
+          <t>08055402382</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1393,32 +1389,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>std256</t>
+          <t>std369</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>MAHMUD</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EFUA</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>AMIRA</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>08033410008</t>
+          <t>07035553555</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1435,32 +1431,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>std257</t>
+          <t>std370</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OMADEFU</t>
+          <t>MOMOH</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ASIBI</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>AMIRA</t>
-        </is>
-      </c>
+          <t>TESLIM</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>08036057258</t>
+          <t>08035877447</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1477,28 +1469,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>std258</t>
+          <t>std371</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ADEYEMI</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HEBBAHTULLAH</t>
+          <t>ABDULMALIK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>08036261741</t>
+          <t>07059477616</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1515,32 +1507,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>std259</t>
+          <t>std372</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DAMUSA</t>
+          <t>USMAN</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UFEDOTOH</t>
+          <t>ISMAIL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NANA K.</t>
+          <t>MUSA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>08065376751</t>
+          <t>07035673797</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1557,32 +1549,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>std260</t>
+          <t>std373</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GALADIMA</t>
+          <t>AHMAD</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USMAN</t>
+          <t>ABUBAKAR</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>KHADIJA</t>
+          <t>JANYAU</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>08144826092</t>
+          <t>07077246902</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1599,28 +1591,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>std261</t>
+          <t>std374</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ABUBAKAR</t>
+          <t>UMAR</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>UMMULKHAIR</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>IDRIS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ATIKU</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>08030569524</t>
+          <t>08026197229</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1637,27 +1633,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>std262</t>
+          <t>std375</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TAJUDEEN</t>
+          <t>ABDULGHAFFAR</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ASIWAJU</t>
+          <t>M.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ABDULBASIT</t>
+          <t>KHALID</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>080095613348</t>
+          <t>09033362393</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1667,7 +1663,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SS2_DIAMOND</t>
+          <t>SS2_SILVER</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1679,37 +1675,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>std263</t>
+          <t>std376</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MUHAMMED</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>OYIZA</t>
+          <t>JAMEEL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>KHAIRET</t>
+          <t>ABUBAKAR</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>08072424291</t>
+          <t>08035573720</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SS2_DIAMOND</t>
+          <t>SS2_SILVER</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1721,23 +1717,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>std264</t>
+          <t>std377</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HABIBULLAH</t>
+          <t>ABDULHAFIZ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ABDULMALIK</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>ISMAIL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>MOMBO</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>08065544064</t>
+          <t>08035972744</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SS2_DIAMOND</t>
+          <t>SS2_SILVER</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1759,23 +1759,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>std265</t>
+          <t>std378</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BABAKURA</t>
+          <t>IBRAHIM</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TIJJANI</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>ALIYU</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>MUSA</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>08067045013</t>
+          <t>08166646064</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1797,23 +1801,27 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>std266</t>
+          <t>std379</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MUSA</t>
+          <t>FAREED</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TAHIR</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>ABDURRASHEED</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ABIOLA</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>08066441344</t>
+          <t>08035553999</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1835,23 +1843,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>std267</t>
+          <t>std380</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>KABIR</t>
+          <t>RAYYAN</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SAIDUBABA</t>
+          <t>OLATUNJI</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>09119851571</t>
+          <t>07030405026</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1873,27 +1881,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>std268</t>
+          <t>std381</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SHEHU</t>
+          <t>MUKTAR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RAMALAN</t>
+          <t>IBRAHIM</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SAABIR</t>
+          <t>ADAM</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>08035927011</t>
+          <t>08066077464</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1915,27 +1923,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>std269</t>
+          <t>std382</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AL-AMIN</t>
+          <t>SA'AD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>O.</t>
+          <t>IDRIS</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AHMED</t>
+          <t>ODARIKO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>08136552705</t>
+          <t>08036330223</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1957,23 +1965,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>std270</t>
+          <t>std383</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ZAHARADEEN</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>UMAR</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>JAMIU</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SULEIMAN</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>08035944688</t>
+          <t>08016685769</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1995,32 +2007,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>std271</t>
+          <t>std384</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AMINU</t>
+          <t>HAFSAT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>UMAR</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>MUSA</t>
+          <t>ZAKARI</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>08032889558</t>
+          <t>080354501362</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2037,32 +2049,28 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>std272</t>
+          <t>std385</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SADIQ</t>
+          <t>BARAKALLAH</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ISMAIL</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>IBRAHIM</t>
-        </is>
-      </c>
+          <t>AKINIBORODE</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>08033587358</t>
+          <t>08032567133</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2079,23 +2087,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>std273</t>
+          <t>std386</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>YUSUF</t>
+          <t>MARYAM</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>JAMILA</t>
+          <t>SULEIMAN</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>08036272740</t>
+          <t>07035501136</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2117,27 +2125,23 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>std274</t>
+          <t>std387</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ABDURRAHMAN</t>
+          <t>BARAKA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NUMAT</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>MAIMUNAT</t>
-        </is>
-      </c>
+          <t>OLAPADE</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>08036040662</t>
+          <t>080169485071</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2159,27 +2163,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>std275</t>
+          <t>std388</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SAMBO</t>
+          <t>NIMAH</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HAJARA</t>
+          <t>MIKAIL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>AMINU</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>08035887544</t>
+          <t>08035559354</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2201,27 +2205,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>std276</t>
+          <t>std389</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SANI</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>YUMNA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>ILIYASU</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>07036576765</t>
+          <t>08036761254</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2243,27 +2247,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>std277</t>
+          <t>std390</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SALISU</t>
+          <t>SABO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NANA</t>
+          <t>AMINA</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ASMAU</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>07089903318</t>
+          <t>07013237225</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2285,27 +2289,23 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>std278</t>
+          <t>std391</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>ABUBAKAR</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ZAINAB</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>AMINU</t>
-        </is>
-      </c>
+          <t>MAIMUNA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>08055262097</t>
+          <t>08023931387</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2327,23 +2327,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>std279</t>
+          <t>std392</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AMATULLAH</t>
+          <t>YAHAYA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ABDULMALIK</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>YASMIN</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>YUNUSA</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>08036495912</t>
+          <t>08025589912</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2365,27 +2369,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>std280</t>
+          <t>std393</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IKAKA</t>
+          <t>HASSAN</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AHMED</t>
+          <t>ASMAU</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>BILKISU</t>
+          <t>ISAH</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>08033884440</t>
+          <t>07035995995</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2407,32 +2411,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>std281</t>
+          <t>std394</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>HAMISU</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>KABIR</t>
+          <t>MUFIDA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>MUKHTAR</t>
+          <t>ZANGO</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>08033912352</t>
+          <t>07036972559</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2449,23 +2453,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>std282</t>
+          <t>std395</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ABDULLAHI</t>
+          <t>MUBARAK</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HUSSAIN</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>IBRAHIM</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>07035663576</t>
+          <t>09031216070</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2487,23 +2495,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>std283</t>
+          <t>std396</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BASHIR</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MAHMUD</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>KABEER</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>IBRAHIM</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>08032181310</t>
+          <t>08003700659</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2525,27 +2537,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>std284</t>
+          <t>std397</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AMINU</t>
+          <t>NASIR</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>YASSAR</t>
+          <t>SA'IDU</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>IBRAHIM</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>08157275454</t>
+          <t>07045077809</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2567,33 +2579,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>std285</t>
+          <t>std398</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>YUSUF</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SA'AD</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>AISHA</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>RABIU</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>08034000882</t>
+          <t>07025646735</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_SILVER</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2605,37 +2621,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>std286</t>
+          <t>std399</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ABAHI</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>WONDA</t>
+          <t>AMADULLAH</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>U. ABDULSAMAD</t>
+          <t>NJOBDI</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>08066188131</t>
+          <t>080025521562</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_SILVER</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2647,37 +2663,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>std287</t>
+          <t>std400</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SHETTIMA</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B.</t>
+          <t>SAFIYA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>MUSTAPHA</t>
+          <t>LOKO</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>08026994119</t>
+          <t>08033441055</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_SILVER</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2689,27 +2705,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>std288</t>
+          <t>std401</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ADEYEMI</t>
+          <t>ABDULHAMEED</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MATTHEW</t>
+          <t>HASSAN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ADESIRE</t>
+          <t>NAIBI</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>08032190197</t>
+          <t>08005127892</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2719,7 +2735,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_SILVER</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2731,23 +2747,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>std289</t>
+          <t>std402</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>KHAIRAT</t>
+          <t>ANISA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BADAMASI</t>
+          <t>NASIR</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>08032245423</t>
+          <t>08135850029</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2757,7 +2773,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_SILVER</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2769,7 +2785,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>std290</t>
+          <t>std403</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2779,13 +2795,13 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SULEIMAN</t>
+          <t>UMAR</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>07029636558</t>
+          <t>09136167237</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2795,7 +2811,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_SILVER</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2807,27 +2823,23 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>std291</t>
+          <t>std404</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ABDULLAHI</t>
+          <t>FA'IZ</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>UMAIMAH</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>ZHEOMA</t>
-        </is>
-      </c>
+          <t>HUSNA</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>08035885141</t>
+          <t>0703300155</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2837,7 +2849,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_SILVER</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2849,27 +2861,23 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>std292</t>
+          <t>std405</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SAED</t>
+          <t>ABDULMUMIN</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ABUBAKAR</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>HASSAN</t>
-        </is>
-      </c>
+          <t>ABDULMALIK</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>08035973912</t>
+          <t>08094974743</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2891,23 +2899,23 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>std293</t>
+          <t>std406</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AKINLOYE</t>
+          <t>OHUI</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GODSWILL</t>
+          <t>MOSES</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>08069353822</t>
+          <t>08128187444</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2929,28 +2937,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>std294</t>
+          <t>std407</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RUKAYYA</t>
+          <t>ABUBAKAR</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>IBRAHIM</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>ALAMIN</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ABDULLAHI</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>08027163415</t>
+          <t>07045413365</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2967,32 +2979,28 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>std295</t>
+          <t>std408</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FARZEENAH</t>
+          <t>ALI</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>T.</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>MUHAMMAD</t>
-        </is>
-      </c>
+          <t>FAHEEM</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>08033577423</t>
+          <t>08065490010</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3009,28 +3017,28 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>std296</t>
+          <t>std409</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>OLAGUNJU</t>
+          <t>DANJUMA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FIRDAUS</t>
+          <t>ARAFAH</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>08138369857</t>
+          <t>09041645172</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3047,28 +3055,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>std297</t>
+          <t>std410</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>OLUFEMOH</t>
+          <t>ABUBAKAR</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MUNIRAT</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>AHMAD</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>PINDAR</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>08026160230</t>
+          <t>08035204272</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3085,32 +3097,28 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>std298</t>
+          <t>std411</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>KHADIJAH</t>
+          <t>AUDU</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BABAYARO</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>MUKHTAR</t>
-        </is>
-      </c>
+          <t>ABDULHAMID</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>07063104355</t>
+          <t>08032741681</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3127,32 +3135,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>std299</t>
+          <t>std412</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SABIRAH</t>
+          <t>AMMDA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>HASSAN</t>
+          <t>ABUBAKAR</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ABDULLAH</t>
+          <t>IMRAN</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>08034204648</t>
+          <t>08038976432</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3169,27 +3177,23 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>std300</t>
+          <t>std413</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ABUBAKAR</t>
+          <t>MUHAMMED</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AMINU</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>SANJUMA</t>
-        </is>
-      </c>
+          <t>HUSSEIN</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>08034132060</t>
+          <t>08037548555</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3211,23 +3215,23 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>std301</t>
+          <t>std414</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>IBRAHIM</t>
+          <t>FARUK</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>TAHIR</t>
+          <t>MUSA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>07035485005</t>
+          <t>08056603644</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3249,27 +3253,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>std302</t>
+          <t>std415</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>KOREDE</t>
+          <t>SHAMSHUDEEN</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SALAU</t>
+          <t>ALIYU</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ABDULLAHI</t>
+          <t>RABO</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>08166294250</t>
+          <t>08131834642</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3291,28 +3295,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>std303</t>
+          <t>std416</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ZANSHIRU</t>
+          <t>HALIMA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>YUSUF</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>IBRAHIM</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>MUSTAPHA</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>08072602070</t>
+          <t>08033550857</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3329,27 +3337,23 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>std304</t>
+          <t>std417</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JUNAIRIYYA</t>
+          <t>BAKO-BABS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>RABIU</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>IDRIS</t>
-        </is>
-      </c>
+          <t>SAMEENA</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>07039229772</t>
+          <t>08027431000</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3371,27 +3375,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>std305</t>
+          <t>std418</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ABUBAKAR</t>
+          <t>OPARIKO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FATIMA</t>
+          <t>SA'ADATU</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>JASMINE</t>
+          <t>IDRIS</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>08033365925</t>
+          <t>08036330773</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3413,32 +3417,28 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>std306</t>
+          <t>std419</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ABDULMALIK</t>
+          <t>BABANGIDA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SAMIR</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>AHMAD</t>
-        </is>
-      </c>
+          <t>UMAR</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>08057265792</t>
+          <t>07017917835</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3455,7 +3455,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>std307</t>
+          <t>std420</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AISHA</t>
+          <t>MARYAM</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>08036173202</t>
+          <t>08033293137</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3497,23 +3497,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>std308</t>
+          <t>std421</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BENITA</t>
+          <t>ABDULLAHI</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PETER</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>AISHA</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>SAMBO</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>08069102556</t>
+          <t>08062843138</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3535,32 +3539,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>std309</t>
+          <t>std422</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ISHAQ</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>A.</t>
+          <t>HAJARA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>QASIM USMAN</t>
+          <t>KABIR</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>08033191149</t>
+          <t>08069453726</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3577,28 +3581,32 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>std310</t>
+          <t>std423</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MUHAMMED</t>
+          <t>NENZAR</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SHEHU</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>REJOICE</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>KASSEM</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>080062447500</t>
+          <t>08139187704</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3615,28 +3623,28 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>std311</t>
+          <t>std424</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LUQMAN</t>
+          <t>YAKUBU</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ALAMIN</t>
+          <t>ASMAUABDULLAHI</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>07032620527</t>
+          <t>08035369624</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3653,23 +3661,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>std312</t>
+          <t>std425</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ABUBAKAR</t>
+          <t>LUKMAN</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>HABIBA</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>MARYAM</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>HANNAFA</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>08041326079</t>
+          <t>07043716151</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3691,23 +3703,23 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>std313</t>
+          <t>std426</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MUSTAPHA</t>
+          <t>ABDULLAHI</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FATIMA</t>
+          <t>HARRAIYA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>08067757775</t>
+          <t>07081365050</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3729,23 +3741,23 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>std314</t>
+          <t>std427</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SANI</t>
+          <t>YUSUF</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FAZEELAT</t>
+          <t>HAFSAH</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>08030799725</t>
+          <t>08036278760</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3755,7 +3767,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SS2_B/C</t>
+          <t>SS2_GOLD</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3767,27 +3779,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>std315</t>
+          <t>std428</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SHOFOLUWE</t>
+          <t>YUSUF</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>O.</t>
+          <t>ASMAU</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NEEMATULLAH</t>
+          <t>JAJI</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>07066229010</t>
+          <t>080698111313</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3797,7 +3809,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SS2_B/C</t>
+          <t>SS2_GOLD</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3809,27 +3821,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>std316</t>
+          <t>std429</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ABBA</t>
+          <t>ABUBAKAR</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MAMMAN</t>
+          <t>AMINA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>FATIMA</t>
+          <t>JANYAU</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>08039725582</t>
+          <t>07077266802</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3839,7 +3851,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SS2_B/C</t>
+          <t>SS2_GOLD</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3851,37 +3863,37 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>std317</t>
+          <t>std430</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FUAD</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ADEYEMI</t>
+          <t>FAUZIYA</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>FAUZI</t>
+          <t>GALADIMA</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>080130680040</t>
+          <t>08039151906</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SS2_B/C</t>
+          <t>SS2_GOLD</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3893,27 +3905,23 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>std318</t>
+          <t>std431</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BASHIR</t>
+          <t>FARUK</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ABDULLAHI</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>MUHAMMAD</t>
-        </is>
-      </c>
+          <t>ABDULKAREEM</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>080372667696</t>
+          <t>08036148800</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3923,7 +3931,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SS2_B/C</t>
+          <t>SS2_GOLD</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3935,37 +3943,33 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>std319</t>
+          <t>std432</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>AHMED</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MARAFIA</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>ATTAHIR</t>
-        </is>
-      </c>
+          <t>AMINA</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0817808006</t>
+          <t>0916301143</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SS2_B/C</t>
+          <t>SS2_GOLD</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3977,37 +3981,33 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>std320</t>
+          <t>std433</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ADEBAYO</t>
+          <t>PIUS</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>DAMILOLA</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>FATHIA</t>
-        </is>
-      </c>
+          <t>GABRIEL</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>090388330432</t>
+          <t>0813224775</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SS2_B/C</t>
+          <t>SS2_GOLD</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4019,27 +4019,23 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>std321</t>
+          <t>std434</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SHAMSU</t>
+          <t>ISSA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ZIYAHULLHAQ</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>MUHAMMAD</t>
-        </is>
-      </c>
+          <t>MUSTAPHA</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>08037031114</t>
+          <t>0806359444</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4049,7 +4045,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SS2_B/C</t>
+          <t>SS2_GOLD</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4061,23 +4057,23 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>std322</t>
+          <t>std435</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JOHN</t>
+          <t>IDOWU</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>ABDULBASIT</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>08034414206</t>
+          <t>08036888250</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4099,23 +4095,23 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>std323</t>
+          <t>std436</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>KOREDE</t>
+          <t>ADEYEMI</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SAMUEL</t>
+          <t>TIAMIYU</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>07053262036</t>
+          <t>08067771845</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4137,23 +4133,27 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>std324</t>
+          <t>std437</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>AJAO</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>UMAR</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
+          <t>SENO</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>HASSAN</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>07034372559</t>
+          <t>07038666604</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4175,27 +4175,27 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>std325</t>
+          <t>std438</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ABDULLAHI</t>
+          <t>AHMAD</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>ZUBAIRU</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ALIYU</t>
+          <t>AHMAD</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>080369891390</t>
+          <t>08033117355</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4217,27 +4217,27 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>std326</t>
+          <t>std439</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>FARUK</t>
+          <t>MUSA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>NDAYAKO</t>
+          <t>UMAR</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SHAFI</t>
+          <t>UMAR</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>08032013860</t>
+          <t>07031940246</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4259,27 +4259,27 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>std327</t>
+          <t>std440</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SANI</t>
+          <t>AMINU</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>WAKILI</t>
+          <t>JAMOH</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>UMAR</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>080331541112</t>
+          <t>07027266014</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4301,32 +4301,28 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>std328</t>
+          <t>std441</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ADEYEMI</t>
+          <t>IBRAHIM</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ADENIKE</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>NAJA'A</t>
-        </is>
-      </c>
+          <t>AUWAL</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>08067371845</t>
+          <t>08077229624</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4343,28 +4339,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>std329</t>
+          <t>std442</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>AJAO</t>
+          <t>TIJJANI</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FAUZIYA</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
+          <t>YAHAYA</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>FAISAL</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>08034372559</t>
+          <t>08036142876</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4381,27 +4381,27 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>std330</t>
+          <t>std443</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ABDULLAHI</t>
+          <t>ALI</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>FOLA</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>SADIQ</t>
+          <t>JAMAL</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>08036989390</t>
+          <t>08065490010</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4423,27 +4423,27 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>std331</t>
+          <t>std444</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>HASHIM</t>
+          <t>KABIR</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MUHAMMED</t>
+          <t>USMAN</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>YUNUS</t>
+          <t>ABDULRAHMAN</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>08094198290</t>
+          <t>08055459291</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4465,28 +4465,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>std332</t>
+          <t>std445</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>UMAR</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
+          <t>TUMALA</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>ZAINAB</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>08037876862</t>
+          <t>08060726243</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4503,23 +4507,27 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>std333</t>
+          <t>std446</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>YUSUF</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>HAUWA</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>BAYERO</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>SA'ADATU</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>080359150327</t>
+          <t>08052144414</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4541,23 +4549,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>std334</t>
+          <t>std447</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SANUSI</t>
+          <t>ABDURRAHMAN</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SUMAYYA</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>NANA</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>FIRDAUSI</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>08059706494</t>
+          <t>08029993984</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4579,27 +4591,27 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>std335</t>
+          <t>std448</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>MAMMAN</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MARYAM</t>
+          <t>YUSHAU</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>MADINAH</t>
+          <t>HAFSAT</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>08188720987</t>
+          <t>08035126935</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4621,32 +4633,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>std336</t>
+          <t>std449</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>AMINU</t>
+          <t>IBRAHIM</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>YASSAR</t>
+          <t>ABDULMUMIN</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>USMAN</t>
+          <t>RAIHANA</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>091338237</t>
+          <t>08032281992</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4663,32 +4675,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>std337</t>
+          <t>std450</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MUSBAHU</t>
+          <t>MURTALA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>YAKUBU</t>
+          <t>FORTY</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>AHMAD</t>
+          <t>FOUR MARZOOQAH</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>080552442908</t>
+          <t>08142244844</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4705,28 +4717,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>std338</t>
+          <t>std451</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ZAYYAN</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MUHSIN</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>ABDUL-AZIZ</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>SALMA</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>07068866548</t>
+          <t>08065486620</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4743,32 +4759,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>std339</t>
+          <t>std452</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ADESHINA</t>
+          <t>ADAM</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CASSANDRA</t>
+          <t>KASIM</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>HABIBA</t>
+          <t>FARUK</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0817251384</t>
+          <t>08033121013</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4785,32 +4801,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>std340</t>
+          <t>std453</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>BASHIR</t>
+          <t>YUSUF</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MAHMUD</t>
+          <t>IBRAHIM</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>HAUWA</t>
+          <t>ADAMU</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>08036587954</t>
+          <t>08032209734</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4827,28 +4843,32 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>std341</t>
+          <t>std454</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ALIYU</t>
+          <t>HASSAN</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AHMAD</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>LODDO</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>HAUWA</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>08085566519</t>
+          <t>07038166600</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4865,32 +4885,32 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>std342</t>
+          <t>std455</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ALIYU</t>
+          <t>YAKUBU</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>LOLO</t>
+          <t>DOMA</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>FATIHA</t>
+          <t>ALIYU SULTAN</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>08035899950</t>
+          <t>08030173092</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4907,32 +4927,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>std343</t>
+          <t>std456</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ALIYU</t>
+          <t>MUSA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SHAFI</t>
+          <t>SHEHU</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>UMAR</t>
+          <t>AISHA</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>0707306375</t>
+          <t>08034918426</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4949,27 +4969,27 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>std344</t>
+          <t>std457</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ALHASSAN</t>
+          <t>GOJI</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AALIYAH</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>UMMT</t>
+          <t>FATIMA</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>080550885141</t>
+          <t>08036257991</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4991,32 +5011,32 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>std345</t>
+          <t>std458</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ABUBAKAR</t>
+          <t>SIAKA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>AMAL</t>
+          <t>SALAMI</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>AISHA</t>
+          <t>JIBRIL</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>0803159021</t>
+          <t>08025512089</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -5033,28 +5053,32 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>std346</t>
+          <t>std459</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SANUSI</t>
+          <t>JIBRIL</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ABDULRAHMAN</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>BILKISU</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>08020850490</t>
+          <t>08033339229</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -5068,8 +5092,176 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>std460</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>IBRAHIM</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>SULEIMURI</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ZAYNAB</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>08035225745</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>SS2_B/C</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>SS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>std461</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>ADETOBO</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ARAFAT</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ADEOLA</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>08054266802</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>SS2_B/C</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>SS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>std462</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>ADAM</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>IDRIS</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>KOGO</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>08036223580</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>SS2_B/C</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>SS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>std463</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>MOHAMMAD</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>HASIZ</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>YUSUF</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>08060683287</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>SS2_B/C</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>SS2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H114"/>
+  <autoFilter ref="A1:H118"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/static/data/database/SS2_Students.xlsx
+++ b/static/data/database/SS2_Students.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SS2 Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SS2 Students'!$A$1:$H$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SS2 Students'!$A$1:$H$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H118"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2861,23 +2861,23 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>std405</t>
+          <t>std435</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ABDULMUMIN</t>
+          <t>IDOWU</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ABDULMALIK</t>
+          <t>ABDULBASIT</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>08094974743</t>
+          <t>08036888250</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2899,23 +2899,23 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>std406</t>
+          <t>std436</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>OHUI</t>
+          <t>ADEYEMI</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MOSES</t>
+          <t>TIAMIYU</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>08128187444</t>
+          <t>08067771845</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2937,27 +2937,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>std407</t>
+          <t>std437</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ABUBAKAR</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ALAMIN</t>
+          <t>SENO</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ABDULLAHI</t>
+          <t>HASSAN</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>07045413365</t>
+          <t>07038666604</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2979,23 +2979,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>std408</t>
+          <t>std438</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ALI</t>
+          <t>AHMAD</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FAHEEM</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>ZUBAIRU</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AHMAD</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>08065490010</t>
+          <t>08033117355</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3005,7 +3009,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3017,23 +3021,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>std409</t>
+          <t>std439</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DANJUMA</t>
+          <t>MUSA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ARAFAH</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>UMAR</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>UMAR</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>09041645172</t>
+          <t>07031940246</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3043,7 +3051,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3055,27 +3063,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>std410</t>
+          <t>std440</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ABUBAKAR</t>
+          <t>AMINU</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AHMAD</t>
+          <t>JAMOH</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>PINDAR</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>08035204272</t>
+          <t>07027266014</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3085,7 +3093,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3097,23 +3105,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>std411</t>
+          <t>std441</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AUDU</t>
+          <t>IBRAHIM</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ABDULHAMID</t>
+          <t>AUWAL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>08032741681</t>
+          <t>08077229624</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3123,7 +3131,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3135,27 +3143,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>std412</t>
+          <t>std442</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AMMDA</t>
+          <t>TIJJANI</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ABUBAKAR</t>
+          <t>YAHAYA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>IMRAN</t>
+          <t>FAISAL</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>08038976432</t>
+          <t>08036142876</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3165,7 +3173,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3177,23 +3185,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>std413</t>
+          <t>std443</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MUHAMMED</t>
+          <t>ALI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>HUSSEIN</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>FOLA</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>JAMAL</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>08037548555</t>
+          <t>08065490010</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3203,7 +3215,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3215,23 +3227,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>std414</t>
+          <t>std444</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FARUK</t>
+          <t>KABIR</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MUSA</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>USMAN</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ABDULRAHMAN</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>08056603644</t>
+          <t>08055459291</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3241,7 +3257,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3253,37 +3269,37 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>std415</t>
+          <t>std445</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SHAMSHUDEEN</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ALIYU</t>
+          <t>TUMALA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>RABO</t>
+          <t>ZAINAB</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>08131834642</t>
+          <t>08060726243</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3295,27 +3311,27 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>std416</t>
+          <t>std446</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HALIMA</t>
+          <t>YUSUF</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IBRAHIM</t>
+          <t>BAYERO</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>MUSTAPHA</t>
+          <t>SA'ADATU</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>08033550857</t>
+          <t>08052144414</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3325,7 +3341,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3337,23 +3353,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>std417</t>
+          <t>std447</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BAKO-BABS</t>
+          <t>ABDURRAHMAN</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SAMEENA</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>NANA</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>FIRDAUSI</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>08027431000</t>
+          <t>08029993984</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3363,7 +3383,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3375,27 +3395,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>std418</t>
+          <t>std448</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>OPARIKO</t>
+          <t>MAMMAN</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SA'ADATU</t>
+          <t>YUSHAU</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>IDRIS</t>
+          <t>HAFSAT</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>08036330773</t>
+          <t>08035126935</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3405,7 +3425,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3417,23 +3437,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>std419</t>
+          <t>std449</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BABANGIDA</t>
+          <t>IBRAHIM</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>UMAR</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>ABDULMUMIN</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>RAIHANA</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>07017917835</t>
+          <t>08032281992</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3443,7 +3467,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3455,27 +3479,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>std420</t>
+          <t>std450</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AUWAL</t>
+          <t>MURTALA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MARYAM</t>
+          <t>FORTY</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>IBRAHIM</t>
+          <t>FOUR MARZOOQAH</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>08033293137</t>
+          <t>08142244844</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3485,7 +3509,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3497,27 +3521,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>std421</t>
+          <t>std451</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ABDULLAHI</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AISHA</t>
+          <t>ABDUL-AZIZ</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>SAMBO</t>
+          <t>SALMA</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>08062843138</t>
+          <t>08065486620</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3527,7 +3551,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3539,37 +3563,37 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>std422</t>
+          <t>std452</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>ADAM</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>HAJARA</t>
+          <t>KASIM</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>KABIR</t>
+          <t>FARUK</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>08069453726</t>
+          <t>08033121013</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3581,37 +3605,37 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>std423</t>
+          <t>std453</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NENZAR</t>
+          <t>YUSUF</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>REJOICE</t>
+          <t>IBRAHIM</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>KASSEM</t>
+          <t>ADAMU</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>08139187704</t>
+          <t>08032209734</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3623,23 +3647,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>std424</t>
+          <t>std454</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>YAKUBU</t>
+          <t>HASSAN</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ASMAUABDULLAHI</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>LODDO</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>HAUWA</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>08035369624</t>
+          <t>07038166600</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3649,7 +3677,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3661,37 +3689,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>std425</t>
+          <t>std455</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LUKMAN</t>
+          <t>YAKUBU</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MARYAM</t>
+          <t>DOMA</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>HANNAFA</t>
+          <t>ALIYU SULTAN</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>07043716151</t>
+          <t>08030173092</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3703,23 +3731,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>std426</t>
+          <t>std456</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ABDULLAHI</t>
+          <t>MUSA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>HARRAIYA</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>SHEHU</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AISHA</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>07081365050</t>
+          <t>08034918426</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3729,7 +3761,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3741,23 +3773,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>std427</t>
+          <t>std457</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>YUSUF</t>
+          <t>GOJI</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>HAFSAH</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>FATIMA</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>08036278760</t>
+          <t>08036257991</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3767,7 +3803,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3779,37 +3815,37 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>std428</t>
+          <t>std458</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>YUSUF</t>
+          <t>SIAKA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ASMAU</t>
+          <t>SALAMI</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>JAJI</t>
+          <t>JIBRIL</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>080698111313</t>
+          <t>08025512089</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3821,27 +3857,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>std429</t>
+          <t>std459</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ABUBAKAR</t>
+          <t>JIBRIL</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AMINA</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>JANYAU</t>
+          <t>BILKISU</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>07077266802</t>
+          <t>08033339229</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3851,7 +3887,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3863,27 +3899,27 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>std430</t>
+          <t>std460</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>IBRAHIM</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FAUZIYA</t>
+          <t>SULEIMURI</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>GALADIMA</t>
+          <t>ZAYNAB</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>08039151906</t>
+          <t>08035225745</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3893,7 +3929,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3905,33 +3941,37 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>std431</t>
+          <t>std461</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FARUK</t>
+          <t>ADETOBO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ABDULKAREEM</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>ARAFAT</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>ADEOLA</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>08036148800</t>
+          <t>08054266802</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3943,33 +3983,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>std432</t>
+          <t>std462</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AHMED</t>
+          <t>ADAM</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AMINA</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
+          <t>IDRIS</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>KOGO</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0916301143</t>
+          <t>08036223580</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3981,23 +4025,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>std433</t>
+          <t>std463</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PIUS</t>
+          <t>MOHAMMAD</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
+          <t>HASIZ</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>YUSUF</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0813224775</t>
+          <t>08060683287</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4007,7 +4055,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SS2_GOLD</t>
+          <t>SS2_B/C</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4016,1252 +4064,8 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>std434</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>ISSA</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>MUSTAPHA</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>0806359444</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>SS2_GOLD</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>std435</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>IDOWU</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>ABDULBASIT</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>08036888250</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>std436</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>ADEYEMI</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>TIAMIYU</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>08067771845</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>std437</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>MUHAMMAD</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>SENO</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>HASSAN</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>07038666604</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>std438</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>AHMAD</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>ZUBAIRU</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>AHMAD</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>08033117355</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>std439</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>MUSA</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>UMAR</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>UMAR</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>07031940246</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>std440</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>AMINU</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>JAMOH</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>MUHAMMAD</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>07027266014</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>std441</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>IBRAHIM</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>AUWAL</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>08077229624</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>std442</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>TIJJANI</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>YAHAYA</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>FAISAL</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>08036142876</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>std443</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>ALI</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>FOLA</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>JAMAL</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>08065490010</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>std444</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>KABIR</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>USMAN</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>ABDULRAHMAN</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>08055459291</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>std445</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>MUHAMMAD</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>TUMALA</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>ZAINAB</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>08060726243</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>std446</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>YUSUF</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>BAYERO</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>SA'ADATU</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>08052144414</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>std447</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>ABDURRAHMAN</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>NANA</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>FIRDAUSI</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>08029993984</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>std448</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>MAMMAN</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>YUSHAU</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>HAFSAT</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>08035126935</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>std449</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>IBRAHIM</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>ABDULMUMIN</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>RAIHANA</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>08032281992</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>std450</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>MURTALA</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>FORTY</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>FOUR MARZOOQAH</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>08142244844</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>std451</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>MUHAMMAD</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>ABDUL-AZIZ</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>SALMA</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>08065486620</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>std452</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>ADAM</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>KASIM</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>FARUK</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>08033121013</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>std453</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>YUSUF</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>IBRAHIM</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>ADAMU</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>08032209734</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>std454</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>HASSAN</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>LODDO</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>HAUWA</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>07038166600</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>std455</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>YAKUBU</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>DOMA</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>ALIYU SULTAN</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>08030173092</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>std456</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>MUSA</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>SHEHU</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>AISHA</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>08034918426</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>std457</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>GOJI</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>MUHAMMAD</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>FATIMA</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>08036257991</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>std458</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>SIAKA</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>SALAMI</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>JIBRIL</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>08025512089</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>std459</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>JIBRIL</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>MUHAMMAD</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>BILKISU</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>08033339229</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>std460</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>IBRAHIM</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>SULEIMURI</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>ZAYNAB</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>08035225745</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>std461</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>ADETOBO</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>ARAFAT</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>ADEOLA</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>08054266802</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>std462</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>ADAM</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>IDRIS</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>KOGO</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>08036223580</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>std463</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>MOHAMMAD</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>HASIZ</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>YUSUF</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>08060683287</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>SS2_B/C</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>SS2</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H118"/>
+  <autoFilter ref="A1:H88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>